--- a/config/excel/Camp.xlsx
+++ b/config/excel/Camp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EF9988-9ED6-4835-B512-4437895D54E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{090DA6CE-4490-4E74-8577-D0098E7309B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19230" yWindow="4395" windowWidth="19995" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20865" yWindow="4485" windowWidth="19995" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfCamp" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
   <si>
     <t>ID</t>
   </si>
@@ -460,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.25" style="1" bestFit="1" customWidth="1"/>
@@ -504,23 +504,56 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C6" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
     </row>

--- a/config/excel/Camp.xlsx
+++ b/config/excel/Camp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{090DA6CE-4490-4E74-8577-D0098E7309B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60206CC7-321F-49B4-AD66-2F8555338DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20865" yWindow="4485" windowWidth="19995" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23400" yWindow="4305" windowWidth="25005" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfCamp" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -74,6 +74,22 @@
   </si>
   <si>
     <t>30,0,10</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>InitMoney</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始金钱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>InitPower</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始电力</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -460,16 +476,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.625" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="13.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -479,8 +497,14 @@
       <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -490,8 +514,14 @@
       <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -501,8 +531,14 @@
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>0</v>
       </c>
@@ -512,8 +548,14 @@
       <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E4" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -523,8 +565,14 @@
       <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E5" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -534,8 +582,14 @@
       <c r="C6" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E6" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>8</v>
       </c>
@@ -545,8 +599,14 @@
       <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>9</v>
       </c>
@@ -555,6 +615,12 @@
       </c>
       <c r="C8" s="3" t="s">
         <v>9</v>
+      </c>
+      <c r="D8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/Camp.xlsx
+++ b/config/excel/Camp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60206CC7-321F-49B4-AD66-2F8555338DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D5FBAF-DA81-47FB-8A30-E9386EA37496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23400" yWindow="4305" windowWidth="25005" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12465" yWindow="3420" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfCamp" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
   <si>
     <t>ID</t>
   </si>
@@ -90,6 +90,14 @@
   </si>
   <si>
     <t>初始电力</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>每秒增加金钱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddMoneyPerSecond</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -476,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.25" style="1" bestFit="1" customWidth="1"/>
@@ -484,10 +492,11 @@
     <col min="3" max="3" width="25.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.25" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="23.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -503,8 +512,11 @@
       <c r="E1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -520,8 +532,11 @@
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -537,8 +552,11 @@
       <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>0</v>
       </c>
@@ -554,8 +572,11 @@
       <c r="E4" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -571,8 +592,11 @@
       <c r="E5" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -588,8 +612,11 @@
       <c r="E6" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>8</v>
       </c>
@@ -605,8 +632,11 @@
       <c r="E7" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>9</v>
       </c>
@@ -621,6 +651,9 @@
       </c>
       <c r="E8" s="3">
         <v>5</v>
+      </c>
+      <c r="F8" s="3">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/Camp.xlsx
+++ b/config/excel/Camp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D5FBAF-DA81-47FB-8A30-E9386EA37496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D497005A-DE70-4789-ABB5-4D872A8433BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12465" yWindow="3420" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="3">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="E8" s="3">
         <v>5</v>

--- a/config/excel/Camp.xlsx
+++ b/config/excel/Camp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D497005A-DE70-4789-ABB5-4D872A8433BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F413DBE-89B9-421B-B6D2-AA220069951E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12465" yWindow="3420" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfCamp" sheetId="1" r:id="rId1"/>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="3">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="E4" s="3">
         <v>5</v>
@@ -587,7 +587,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="3">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="E5" s="3">
         <v>5</v>
@@ -607,7 +607,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="3">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="E6" s="3">
         <v>5</v>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="3">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="E7" s="3">
         <v>5</v>

--- a/config/excel/Camp.xlsx
+++ b/config/excel/Camp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F413DBE-89B9-421B-B6D2-AA220069951E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D81A43-B24C-443A-8322-5ADF7D1BDD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22050" yWindow="3885" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfCamp" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
   <si>
     <t>ID</t>
   </si>
@@ -98,6 +98,14 @@
   </si>
   <si>
     <t>AddMoneyPerSecond</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HealDelayTick</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动回血的冷却时间</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -484,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.25" style="1" bestFit="1" customWidth="1"/>
@@ -493,10 +501,11 @@
     <col min="4" max="4" width="13.25" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -515,8 +524,11 @@
       <c r="F1" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -535,8 +547,11 @@
       <c r="F2" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -555,8 +570,11 @@
       <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>0</v>
       </c>
@@ -575,8 +593,11 @@
       <c r="F4" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -595,8 +616,11 @@
       <c r="F5" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -615,8 +639,11 @@
       <c r="F6" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>8</v>
       </c>
@@ -635,8 +662,11 @@
       <c r="F7" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>9</v>
       </c>
@@ -654,6 +684,9 @@
       </c>
       <c r="F8" s="3">
         <v>15</v>
+      </c>
+      <c r="G8" s="3">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/Camp.xlsx
+++ b/config/excel/Camp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D81A43-B24C-443A-8322-5ADF7D1BDD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E531DD91-FDF6-4DBD-93E6-77F01D706D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22050" yWindow="3885" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="2595" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfCamp" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
   <si>
     <t>ID</t>
   </si>
@@ -57,26 +57,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>10,0,30</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>115,0,95</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>VehicleFactoryPosition</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>95,0,115</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>30,0,10</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>InitMoney</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -106,6 +90,22 @@
   </si>
   <si>
     <t>自动回血的冷却时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,0,40</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>40,0,20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>85,0,105</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>105,0,85</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -492,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.25" style="1" bestFit="1" customWidth="1"/>
@@ -513,19 +513,19 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -562,27 +562,27 @@
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3">
         <v>8000</v>
@@ -591,7 +591,7 @@
         <v>5</v>
       </c>
       <c r="F4" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G4" s="3">
         <v>150</v>
@@ -599,13 +599,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D5" s="3">
         <v>8000</v>
@@ -614,7 +614,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G5" s="3">
         <v>150</v>
@@ -622,70 +622,24 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D6" s="3">
-        <v>8000</v>
+        <v>3000</v>
       </c>
       <c r="E6" s="3">
         <v>5</v>
       </c>
       <c r="F6" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G6" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="3">
-        <v>8000</v>
-      </c>
-      <c r="E7" s="3">
-        <v>5</v>
-      </c>
-      <c r="F7" s="3">
-        <v>15</v>
-      </c>
-      <c r="G7" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>9</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="3">
-        <v>3000</v>
-      </c>
-      <c r="E8" s="3">
-        <v>5</v>
-      </c>
-      <c r="F8" s="3">
-        <v>15</v>
-      </c>
-      <c r="G8" s="3">
         <v>150</v>
       </c>
     </row>

--- a/config/excel/Camp.xlsx
+++ b/config/excel/Camp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E531DD91-FDF6-4DBD-93E6-77F01D706D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816DB2A4-D390-444D-AF45-ECF24702CCCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="2595" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfCamp" sheetId="1" r:id="rId1"/>
@@ -585,7 +585,7 @@
         <v>16</v>
       </c>
       <c r="D4" s="3">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="E4" s="3">
         <v>5</v>
@@ -608,7 +608,7 @@
         <v>17</v>
       </c>
       <c r="D5" s="3">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="E5" s="3">
         <v>5</v>

--- a/config/excel/Camp.xlsx
+++ b/config/excel/Camp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816DB2A4-D390-444D-AF45-ECF24702CCCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86897CED-EC09-4A02-869C-4EE02170A2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8235" yWindow="2280" windowWidth="34560" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfCamp" sheetId="1" r:id="rId1"/>
@@ -585,7 +585,7 @@
         <v>16</v>
       </c>
       <c r="D4" s="3">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="E4" s="3">
         <v>5</v>
@@ -608,7 +608,7 @@
         <v>17</v>
       </c>
       <c r="D5" s="3">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="E5" s="3">
         <v>5</v>
@@ -631,7 +631,7 @@
         <v>17</v>
       </c>
       <c r="D6" s="3">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="E6" s="3">
         <v>5</v>

--- a/config/excel/Camp.xlsx
+++ b/config/excel/Camp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86897CED-EC09-4A02-869C-4EE02170A2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903E7EB2-3430-4455-ACE3-DE4287D8F404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8235" yWindow="2280" windowWidth="34560" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7890" yWindow="1935" windowWidth="34560" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfCamp" sheetId="1" r:id="rId1"/>
@@ -65,22 +65,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>初始金钱</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>InitPower</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>初始电力</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>每秒增加金钱</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>AddMoneyPerSecond</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -106,6 +94,18 @@
   </si>
   <si>
     <t>105,0,85</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始金币</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始能量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>每秒增加金币</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -519,13 +519,13 @@
         <v>7</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="G1" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -562,16 +562,16 @@
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -579,19 +579,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="E4" s="3">
         <v>5</v>
       </c>
       <c r="F4" s="3">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G4" s="3">
         <v>150</v>
@@ -602,19 +602,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="E5" s="3">
         <v>5</v>
       </c>
       <c r="F5" s="3">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G5" s="3">
         <v>150</v>
@@ -625,19 +625,19 @@
         <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D6" s="3">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="E6" s="3">
         <v>5</v>
       </c>
       <c r="F6" s="3">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G6" s="3">
         <v>150</v>
